--- a/src/db_compilation_orov/inputs/outbreaks_orov.xlsx
+++ b/src/db_compilation_orov/inputs/outbreaks_orov.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/rom116_ic_ac_uk/Documents/Oropouche/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rom116\Documents\github\priority-pathogens\src\db_compilation_orov\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A37E3361-5375-4902-AB52-5F4347283D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED7FDA7-4D48-4E4B-85A1-7D46D458DABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{8EBA00C0-5507-46D1-97BC-5AB48D4DE660}"/>
   </bookViews>
@@ -1438,9 +1438,9 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2390,7 +2390,7 @@
         <v>45</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>44</v>
@@ -5665,7 +5665,7 @@
         <v>44</v>
       </c>
       <c r="AB30" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC30" s="1" t="s">
         <v>44</v>
@@ -5796,7 +5796,7 @@
         <v>44</v>
       </c>
       <c r="AB31" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC31" s="1" t="s">
         <v>44</v>
@@ -6451,7 +6451,7 @@
         <v>44</v>
       </c>
       <c r="AB36" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC36" s="1" t="s">
         <v>44</v>
@@ -6582,7 +6582,7 @@
         <v>44</v>
       </c>
       <c r="AB37" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC37" s="1" t="s">
         <v>44</v>
@@ -6713,7 +6713,7 @@
         <v>44</v>
       </c>
       <c r="AB38" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC38" s="1" t="s">
         <v>44</v>
@@ -6844,7 +6844,7 @@
         <v>44</v>
       </c>
       <c r="AB39" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC39" s="1" t="s">
         <v>44</v>
@@ -6975,7 +6975,7 @@
         <v>44</v>
       </c>
       <c r="AB40" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC40" s="1" t="s">
         <v>44</v>
@@ -7106,7 +7106,7 @@
         <v>44</v>
       </c>
       <c r="AB41" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC41" s="1" t="s">
         <v>44</v>
@@ -7237,7 +7237,7 @@
         <v>44</v>
       </c>
       <c r="AB42" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC42" s="1" t="s">
         <v>44</v>
@@ -7368,7 +7368,7 @@
         <v>44</v>
       </c>
       <c r="AB43" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC43" s="1" t="s">
         <v>44</v>
@@ -7499,7 +7499,7 @@
         <v>44</v>
       </c>
       <c r="AB44" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC44" s="1" t="s">
         <v>44</v>
@@ -7630,7 +7630,7 @@
         <v>44</v>
       </c>
       <c r="AB45" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC45" s="1" t="s">
         <v>44</v>
@@ -7761,7 +7761,7 @@
         <v>44</v>
       </c>
       <c r="AB46" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC46" s="1" t="s">
         <v>44</v>
@@ -7892,7 +7892,7 @@
         <v>44</v>
       </c>
       <c r="AB47" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC47" s="1" t="s">
         <v>44</v>
@@ -8023,7 +8023,7 @@
         <v>44</v>
       </c>
       <c r="AB48" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC48" s="1" t="s">
         <v>44</v>
@@ -8154,7 +8154,7 @@
         <v>44</v>
       </c>
       <c r="AB49" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC49" s="1" t="s">
         <v>44</v>
@@ -8285,7 +8285,7 @@
         <v>44</v>
       </c>
       <c r="AB50" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC50" s="1" t="s">
         <v>44</v>
@@ -8416,7 +8416,7 @@
         <v>44</v>
       </c>
       <c r="AB51" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC51" s="1" t="s">
         <v>44</v>
@@ -8547,7 +8547,7 @@
         <v>44</v>
       </c>
       <c r="AB52" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC52" s="1" t="s">
         <v>44</v>
@@ -8678,7 +8678,7 @@
         <v>44</v>
       </c>
       <c r="AB53" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC53" s="1" t="s">
         <v>44</v>
@@ -8809,7 +8809,7 @@
         <v>44</v>
       </c>
       <c r="AB54" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC54" s="1" t="s">
         <v>44</v>
@@ -8940,7 +8940,7 @@
         <v>44</v>
       </c>
       <c r="AB55" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC55" s="1" t="s">
         <v>44</v>
@@ -9071,7 +9071,7 @@
         <v>44</v>
       </c>
       <c r="AB56" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC56" s="1" t="s">
         <v>44</v>
@@ -9202,7 +9202,7 @@
         <v>44</v>
       </c>
       <c r="AB57" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC57" s="1" t="s">
         <v>44</v>
@@ -9333,7 +9333,7 @@
         <v>44</v>
       </c>
       <c r="AB58" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC58" s="1" t="s">
         <v>44</v>
@@ -9464,7 +9464,7 @@
         <v>44</v>
       </c>
       <c r="AB59" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC59" s="1" t="s">
         <v>44</v>
@@ -9595,7 +9595,7 @@
         <v>44</v>
       </c>
       <c r="AB60" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC60" s="1" t="s">
         <v>44</v>
@@ -9726,7 +9726,7 @@
         <v>44</v>
       </c>
       <c r="AB61" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC61" s="1" t="s">
         <v>44</v>
@@ -18002,7 +18002,7 @@
         <v>44</v>
       </c>
       <c r="AB125" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC125" s="1" t="s">
         <v>44</v>
@@ -18133,7 +18133,7 @@
         <v>44</v>
       </c>
       <c r="AB126" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC126" s="1" t="s">
         <v>44</v>
@@ -18264,7 +18264,7 @@
         <v>44</v>
       </c>
       <c r="AB127" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC127" s="1" t="s">
         <v>44</v>
@@ -18395,7 +18395,7 @@
         <v>44</v>
       </c>
       <c r="AB128" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC128" s="1" t="s">
         <v>44</v>
@@ -18526,7 +18526,7 @@
         <v>44</v>
       </c>
       <c r="AB129" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC129" s="1" t="s">
         <v>44</v>
@@ -18657,7 +18657,7 @@
         <v>44</v>
       </c>
       <c r="AB130" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC130" s="1" t="s">
         <v>44</v>
@@ -18788,7 +18788,7 @@
         <v>44</v>
       </c>
       <c r="AB131" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC131" s="1" t="s">
         <v>44</v>
@@ -18919,7 +18919,7 @@
         <v>44</v>
       </c>
       <c r="AB132" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC132" s="1" t="s">
         <v>44</v>
@@ -19050,7 +19050,7 @@
         <v>44</v>
       </c>
       <c r="AB133" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC133" s="1" t="s">
         <v>44</v>
@@ -19312,7 +19312,7 @@
         <v>45</v>
       </c>
       <c r="AB135" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC135" s="1" t="s">
         <v>44</v>
@@ -19443,7 +19443,7 @@
         <v>44</v>
       </c>
       <c r="AB136" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC136" s="1" t="s">
         <v>44</v>
@@ -19574,7 +19574,7 @@
         <v>44</v>
       </c>
       <c r="AB137" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC137" s="1" t="s">
         <v>44</v>
@@ -19705,7 +19705,7 @@
         <v>44</v>
       </c>
       <c r="AB138" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC138" s="1" t="s">
         <v>44</v>
@@ -19836,7 +19836,7 @@
         <v>44</v>
       </c>
       <c r="AB139" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC139" s="1" t="s">
         <v>44</v>
@@ -19967,7 +19967,7 @@
         <v>44</v>
       </c>
       <c r="AB140" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC140" s="1" t="s">
         <v>44</v>
@@ -20098,7 +20098,7 @@
         <v>44</v>
       </c>
       <c r="AB141" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC141" s="1" t="s">
         <v>44</v>
@@ -20229,7 +20229,7 @@
         <v>44</v>
       </c>
       <c r="AB142" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC142" s="1" t="s">
         <v>44</v>
@@ -20360,7 +20360,7 @@
         <v>44</v>
       </c>
       <c r="AB143" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC143" s="1" t="s">
         <v>44</v>
@@ -20491,7 +20491,7 @@
         <v>44</v>
       </c>
       <c r="AB144" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC144" s="1" t="s">
         <v>44</v>
@@ -20622,7 +20622,7 @@
         <v>44</v>
       </c>
       <c r="AB145" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC145" s="1" t="s">
         <v>44</v>
@@ -20753,7 +20753,7 @@
         <v>44</v>
       </c>
       <c r="AB146" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC146" s="1" t="s">
         <v>44</v>
@@ -23719,6 +23719,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AQ169" xr:uid="{40A050C1-5F04-4154-94B7-59D3A2998759}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>